--- a/healthcare_surveys/025_elder_care_technology_adoption_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/025_elder_care_technology_adoption_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'primary_caregiver'}</t>
+          <t>primary_caregiver</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'primary caregiver'}</t>
+          <t>primary caregiver</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'secondary_caregiver'}</t>
+          <t>secondary_caregiver</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'secondary caregiver'}</t>
+          <t>secondary caregiver</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'basic_care'}</t>
+          <t>basic_care</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'basic care'}</t>
+          <t>basic care</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'skilled_care'}</t>
+          <t>skilled_care</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'skilled care'}</t>
+          <t>skilled care</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'custodial_care'}</t>
+          <t>custodial_care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'custodial care'}</t>
+          <t>custodial care</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'smart_home'}</t>
+          <t>smart_home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'smart home'}</t>
+          <t>smart home</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'telecare'}</t>
+          <t>telecare</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'telecare'}</t>
+          <t>telecare</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'video_monitoring'}</t>
+          <t>video_monitoring</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'video monitoring'}</t>
+          <t>video monitoring</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'improved_quality_of_care'}</t>
+          <t>improved_quality_of_care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'improved quality of care'}</t>
+          <t>improved quality of care</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cost_savings'}</t>
+          <t>cost_savings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'cost savings'}</t>
+          <t>cost savings</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'enhanced_caregiver_engagement'}</t>
+          <t>enhanced_caregiver_engagement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'enhanced caregiver engagement'}</t>
+          <t>enhanced caregiver engagement</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'training'}</t>
+          <t>training</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'adoption'}</t>
+          <t>adoption</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'adoption'}</t>
+          <t>adoption</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'both'}</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'carequal'}</t>
+          <t>carequal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'carequal'}</t>
+          <t>carequal</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
